--- a/datos_Grup D.xlsx
+++ b/datos_Grup D.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,16 +525,6 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Increment_x</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Increment_y</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
           <t>Increment</t>
         </is>
       </c>
@@ -604,7 +594,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3212.27</v>
+        <v>2974.32</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>31373</v>
@@ -615,14 +605,6 @@
       <c r="S2" t="n">
         <v>0.08</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -689,7 +671,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3480.54</v>
+        <v>3222.72</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>28414</v>
@@ -700,14 +682,6 @@
       <c r="S3" t="n">
         <v>0.08</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -774,7 +748,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3111.96</v>
+        <v>2881.44</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>18528</v>
@@ -785,14 +759,6 @@
       <c r="S4" t="n">
         <v>0.08</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -859,7 +825,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3240.26</v>
+        <v>3000.24</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>33205</v>
@@ -870,14 +836,6 @@
       <c r="S5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -944,7 +902,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3515.53</v>
+        <v>3255.12</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>36491</v>
@@ -955,14 +913,6 @@
       <c r="S6" t="n">
         <v>0.08</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1029,7 +979,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3214.6</v>
+        <v>2976.48</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>29743</v>
@@ -1040,14 +990,6 @@
       <c r="S7" t="n">
         <v>0.08</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1114,7 +1056,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3703.32</v>
+        <v>3429</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>25319</v>
@@ -1125,14 +1067,6 @@
       <c r="S8" t="n">
         <v>0.08</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1199,7 +1133,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3295.08</v>
+        <v>3051</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>32132</v>
@@ -1210,14 +1144,6 @@
       <c r="S9" t="n">
         <v>0.08</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1284,7 +1210,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3129.45</v>
+        <v>2897.64</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>37896</v>
@@ -1295,14 +1221,6 @@
       <c r="S10" t="n">
         <v>0.08</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1369,7 +1287,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3381.39</v>
+        <v>3130.92</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>38657</v>
@@ -1380,14 +1298,6 @@
       <c r="S11" t="n">
         <v>0.08</v>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1454,7 +1364,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2855.35</v>
+        <v>2643.84</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>18372</v>
@@ -1465,14 +1375,6 @@
       <c r="S12" t="n">
         <v>0.08</v>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1539,7 +1441,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2837.85</v>
+        <v>2627.64</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>32349</v>
@@ -1550,14 +1452,6 @@
       <c r="S13" t="n">
         <v>0.08</v>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1624,7 +1518,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3457.21</v>
+        <v>3201.12</v>
       </c>
       <c r="Q14" s="2" t="n">
         <v>26516</v>
@@ -1635,14 +1529,6 @@
       <c r="S14" t="n">
         <v>0.08</v>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1709,7 +1595,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3882.95</v>
+        <v>3595.32</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>18805</v>
@@ -1720,14 +1606,6 @@
       <c r="S15" t="n">
         <v>0.08</v>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1794,7 +1672,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3443.21</v>
+        <v>3188.16</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>19560</v>
@@ -1805,14 +1683,6 @@
       <c r="S16" t="n">
         <v>0.08</v>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1879,7 +1749,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3045.47</v>
+        <v>2819.88</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>19709</v>
@@ -1890,14 +1760,6 @@
       <c r="S17" t="n">
         <v>0.08</v>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1964,7 +1826,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3277.58</v>
+        <v>3034.8</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>37021</v>
@@ -1975,14 +1837,6 @@
       <c r="S18" t="n">
         <v>0.08</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2049,7 +1903,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3027.97</v>
+        <v>2803.68</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>22446</v>
@@ -2060,14 +1914,6 @@
       <c r="S19" t="n">
         <v>0.08</v>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2134,7 +1980,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3124.79</v>
+        <v>2893.32</v>
       </c>
       <c r="Q20" s="2" t="n">
         <v>33071</v>
@@ -2145,14 +1991,6 @@
       <c r="S20" t="n">
         <v>0.08</v>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2219,7 +2057,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3365.06</v>
+        <v>3115.8</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>33856</v>
@@ -2230,14 +2068,6 @@
       <c r="S21" t="n">
         <v>0.08</v>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2304,7 +2134,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3324.24</v>
+        <v>3078</v>
       </c>
       <c r="Q22" s="2" t="n">
         <v>26744</v>
@@ -2315,14 +2145,6 @@
       <c r="S22" t="n">
         <v>0.08</v>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2385,7 +2207,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3198.27</v>
+        <v>2961.36</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>29718</v>
@@ -2396,14 +2218,6 @@
       <c r="S23" t="n">
         <v>0.08</v>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2470,7 +2284,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3248.42</v>
+        <v>3007.8</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>36833</v>
@@ -2481,14 +2295,6 @@
       <c r="S24" t="n">
         <v>0.08</v>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2555,7 +2361,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3290.41</v>
+        <v>3046.68</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>30677</v>
@@ -2566,14 +2372,6 @@
       <c r="S25" t="n">
         <v>0.08</v>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2636,7 +2434,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3394.22</v>
+        <v>3142.8</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>27830</v>
@@ -2647,14 +2445,6 @@
       <c r="S26" t="n">
         <v>0.08</v>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U26" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2721,7 +2511,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3800.13</v>
+        <v>3518.64</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>34875</v>
@@ -2732,14 +2522,6 @@
       <c r="S27" t="n">
         <v>0.08</v>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2806,7 +2588,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3664.83</v>
+        <v>3393.36</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>37530</v>
@@ -2817,14 +2599,6 @@
       <c r="S28" t="n">
         <v>0.08</v>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2887,7 +2661,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3050.14</v>
+        <v>2824.2</v>
       </c>
       <c r="Q29" s="2" t="n">
         <v>26158</v>
@@ -2898,14 +2672,6 @@
       <c r="S29" t="n">
         <v>0.08</v>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2972,7 +2738,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3914.44</v>
+        <v>3624.48</v>
       </c>
       <c r="Q30" s="2" t="n">
         <v>31881</v>
@@ -2983,14 +2749,6 @@
       <c r="S30" t="n">
         <v>0.08</v>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3057,7 +2815,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3798.96</v>
+        <v>3517.56</v>
       </c>
       <c r="Q31" s="2" t="n">
         <v>34770</v>
@@ -3068,14 +2826,6 @@
       <c r="S31" t="n">
         <v>0.08</v>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3142,7 +2892,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3225.1</v>
+        <v>2986.2</v>
       </c>
       <c r="Q32" s="2" t="n">
         <v>38177</v>
@@ -3153,14 +2903,6 @@
       <c r="S32" t="n">
         <v>0.08</v>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3227,7 +2969,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3545.86</v>
+        <v>3283.2</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>28338</v>
@@ -3238,14 +2980,6 @@
       <c r="S33" t="n">
         <v>0.08</v>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U33" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3312,7 +3046,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3337.07</v>
+        <v>3089.88</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>22893</v>
@@ -3323,14 +3057,6 @@
       <c r="S34" t="n">
         <v>0.08</v>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U34" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3393,7 +3119,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3463.04</v>
+        <v>3206.52</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>31816</v>
@@ -3404,14 +3130,6 @@
       <c r="S35" t="n">
         <v>0.08</v>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U35" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3478,7 +3196,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2794.69</v>
+        <v>2587.68</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>31657</v>
@@ -3489,14 +3207,6 @@
       <c r="S36" t="n">
         <v>0.08</v>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U36" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3563,7 +3273,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3470.04</v>
+        <v>3213</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>26118</v>
@@ -3574,14 +3284,6 @@
       <c r="S37" t="n">
         <v>0.08</v>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U37" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3648,7 +3350,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3361.56</v>
+        <v>3112.56</v>
       </c>
       <c r="Q38" s="2" t="n">
         <v>32577</v>
@@ -3659,14 +3361,6 @@
       <c r="S38" t="n">
         <v>0.08</v>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U38" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3733,7 +3427,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3067.63</v>
+        <v>2840.4</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>21947</v>
@@ -3744,14 +3438,6 @@
       <c r="S39" t="n">
         <v>0.08</v>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U39" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3818,23 +3504,15 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3829.29</v>
+        <v>3545.64</v>
       </c>
       <c r="Q40" s="2" t="n">
         <v>28545</v>
       </c>
       <c r="R40" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U40" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -3903,7 +3581,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3255.42</v>
+        <v>3014.28</v>
       </c>
       <c r="Q41" s="2" t="n">
         <v>35902</v>
@@ -3914,14 +3592,6 @@
       <c r="S41" t="n">
         <v>0.08</v>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U41" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3988,7 +3658,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3038.47</v>
+        <v>2813.4</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>32956</v>
@@ -3999,14 +3669,6 @@
       <c r="S42" t="n">
         <v>0.08</v>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U42" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4073,7 +3735,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3870.12</v>
+        <v>3583.44</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>31461</v>
@@ -4084,14 +3746,6 @@
       <c r="S43" t="n">
         <v>0.08</v>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U43" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4158,7 +3812,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3442.05</v>
+        <v>3187.08</v>
       </c>
       <c r="Q44" s="2" t="n">
         <v>20885</v>
@@ -4169,14 +3823,6 @@
       <c r="S44" t="n">
         <v>0.08</v>
       </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U44" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4243,7 +3889,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3402.39</v>
+        <v>3150.36</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>18676</v>
@@ -4254,14 +3900,6 @@
       <c r="S45" t="n">
         <v>0.08</v>
       </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U45" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4328,7 +3966,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3523.69</v>
+        <v>3262.68</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>27033</v>
@@ -4339,14 +3977,6 @@
       <c r="S46" t="n">
         <v>0.08</v>
       </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U46" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4413,7 +4043,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3794.3</v>
+        <v>3513.24</v>
       </c>
       <c r="Q47" s="2" t="n">
         <v>25592</v>
@@ -4424,14 +4054,6 @@
       <c r="S47" t="n">
         <v>0.08</v>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U47" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4498,7 +4120,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3388.39</v>
+        <v>3137.4</v>
       </c>
       <c r="Q48" s="2" t="n">
         <v>23448</v>
@@ -4509,14 +4131,6 @@
       <c r="S48" t="n">
         <v>0.08</v>
       </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U48" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4583,7 +4197,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3501.53</v>
+        <v>3242.16</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>30050</v>
@@ -4594,14 +4208,6 @@
       <c r="S49" t="n">
         <v>0.08</v>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U49" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4668,7 +4274,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3103.79</v>
+        <v>2873.88</v>
       </c>
       <c r="Q50" s="2" t="n">
         <v>27262</v>
@@ -4679,14 +4285,6 @@
       <c r="S50" t="n">
         <v>0.08</v>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U50" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4753,7 +4351,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3467.71</v>
+        <v>3210.84</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>25789</v>
@@ -4764,14 +4362,6 @@
       <c r="S51" t="n">
         <v>0.08</v>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U51" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4838,7 +4428,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3340.57</v>
+        <v>3093.12</v>
       </c>
       <c r="Q52" s="2" t="n">
         <v>36870</v>
@@ -4849,14 +4439,6 @@
       <c r="S52" t="n">
         <v>0.08</v>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U52" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4923,7 +4505,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3438.55</v>
+        <v>3183.84</v>
       </c>
       <c r="Q53" s="2" t="n">
         <v>38282</v>
@@ -4934,14 +4516,6 @@
       <c r="S53" t="n">
         <v>0.08</v>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U53" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5008,7 +4582,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3094.46</v>
+        <v>2865.24</v>
       </c>
       <c r="Q54" s="2" t="n">
         <v>21258</v>
@@ -5019,14 +4593,6 @@
       <c r="S54" t="n">
         <v>0.08</v>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5089,7 +4655,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3375.56</v>
+        <v>3125.52</v>
       </c>
       <c r="Q55" s="2" t="n">
         <v>34216</v>
@@ -5100,14 +4666,6 @@
       <c r="S55" t="n">
         <v>0.08</v>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5174,7 +4732,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2771.37</v>
+        <v>2566.08</v>
       </c>
       <c r="Q56" s="2" t="n">
         <v>38285</v>
@@ -5183,14 +4741,6 @@
         <v>21</v>
       </c>
       <c r="S56" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
         <v>0.08</v>
       </c>
     </row>
